--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/17.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/17.xlsx
@@ -426,13 +426,13 @@
         <v>-10.11615446212055</v>
       </c>
       <c r="E2">
-        <v>-21.57742899657158</v>
+        <v>-25.8622892165253</v>
       </c>
       <c r="F2">
-        <v>-3.66479197111644</v>
+        <v>-3.605125495460194</v>
       </c>
       <c r="G2">
-        <v>-14.02750264421515</v>
+        <v>-16.46928158088863</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.886262678797978</v>
       </c>
       <c r="E3">
-        <v>-21.73687203790765</v>
+        <v>-26.20519885380813</v>
       </c>
       <c r="F3">
-        <v>-3.541834084049298</v>
+        <v>-3.501842162576943</v>
       </c>
       <c r="G3">
-        <v>-14.04096828819613</v>
+        <v>-16.22178023055441</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.522695483240115</v>
       </c>
       <c r="E4">
-        <v>-22.91563835057825</v>
+        <v>-26.30744273995331</v>
       </c>
       <c r="F4">
-        <v>-3.39465804759391</v>
+        <v>-3.317142739509543</v>
       </c>
       <c r="G4">
-        <v>-14.30319163454349</v>
+        <v>-15.31545548881367</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.041688085768726</v>
       </c>
       <c r="E5">
-        <v>-22.75758555076254</v>
+        <v>-27.3171747033396</v>
       </c>
       <c r="F5">
-        <v>-3.51687868767256</v>
+        <v>-3.234765743138146</v>
       </c>
       <c r="G5">
-        <v>-14.01914186145572</v>
+        <v>-15.68751611506297</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.447891655662177</v>
       </c>
       <c r="E6">
-        <v>-23.14548557731156</v>
+        <v>-26.62960290933298</v>
       </c>
       <c r="F6">
-        <v>-3.363862661027435</v>
+        <v>-3.173029177342305</v>
       </c>
       <c r="G6">
-        <v>-14.48576987630707</v>
+        <v>-16.10843873819915</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.761883725466585</v>
       </c>
       <c r="E7">
-        <v>-22.99611386216856</v>
+        <v>-27.2588479581208</v>
       </c>
       <c r="F7">
-        <v>-3.205720696893787</v>
+        <v>-3.351136452618226</v>
       </c>
       <c r="G7">
-        <v>-14.03339707054782</v>
+        <v>-15.94640243150675</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.008326718106437</v>
       </c>
       <c r="E8">
-        <v>-23.96646621558415</v>
+        <v>-27.73742614819942</v>
       </c>
       <c r="F8">
-        <v>-3.266836815504932</v>
+        <v>-3.354675238162986</v>
       </c>
       <c r="G8">
-        <v>-14.18301386564964</v>
+        <v>-15.83364359516641</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.207283079420112</v>
       </c>
       <c r="E9">
-        <v>-24.24916526246098</v>
+        <v>-28.24633152870741</v>
       </c>
       <c r="F9">
-        <v>-3.131466671274242</v>
+        <v>-3.201627733556555</v>
       </c>
       <c r="G9">
-        <v>-14.1553178416681</v>
+        <v>-15.5446726961345</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.375741242155525</v>
       </c>
       <c r="E10">
-        <v>-24.54610183161794</v>
+        <v>-28.79775022319941</v>
       </c>
       <c r="F10">
-        <v>-3.203983610450117</v>
+        <v>-3.287989177135417</v>
       </c>
       <c r="G10">
-        <v>-14.13034639666537</v>
+        <v>-15.81097132404071</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.538896721306132</v>
       </c>
       <c r="E11">
-        <v>-25.69214539110911</v>
+        <v>-29.04317992899312</v>
       </c>
       <c r="F11">
-        <v>-3.140519070252036</v>
+        <v>-3.206045416915685</v>
       </c>
       <c r="G11">
-        <v>-13.38262658116558</v>
+        <v>-14.92637203740144</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.711358415429284</v>
       </c>
       <c r="E12">
-        <v>-26.50411436610643</v>
+        <v>-29.63339406030883</v>
       </c>
       <c r="F12">
-        <v>-2.983864025606413</v>
+        <v>-3.000864609814067</v>
       </c>
       <c r="G12">
-        <v>-13.29513548365373</v>
+        <v>-15.13573590312326</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.899250099641879</v>
       </c>
       <c r="E13">
-        <v>-26.58182298007805</v>
+        <v>-30.36773140539265</v>
       </c>
       <c r="F13">
-        <v>-2.878611663406707</v>
+        <v>-2.870047172829163</v>
       </c>
       <c r="G13">
-        <v>-13.36976511174552</v>
+        <v>-15.19129513363608</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.121393761330255</v>
       </c>
       <c r="E14">
-        <v>-27.33443724625684</v>
+        <v>-30.86070335010465</v>
       </c>
       <c r="F14">
-        <v>-2.880810150493737</v>
+        <v>-2.834842386577587</v>
       </c>
       <c r="G14">
-        <v>-12.76700415377379</v>
+        <v>-14.78560101998055</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.387054183446274</v>
       </c>
       <c r="E15">
-        <v>-28.44663951948869</v>
+        <v>-31.28913774749633</v>
       </c>
       <c r="F15">
-        <v>-2.83699448509006</v>
+        <v>-2.841402228040356</v>
       </c>
       <c r="G15">
-        <v>-11.98085552565414</v>
+        <v>-14.40115564286883</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6975152902440021</v>
       </c>
       <c r="E16">
-        <v>-28.92005977767258</v>
+        <v>-32.03160596766093</v>
       </c>
       <c r="F16">
-        <v>-2.320101509417197</v>
+        <v>-2.558084008934869</v>
       </c>
       <c r="G16">
-        <v>-12.16663009913588</v>
+        <v>-14.20368491199685</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.06388530286059879</v>
       </c>
       <c r="E17">
-        <v>-29.89478210850557</v>
+        <v>-33.04462786741379</v>
       </c>
       <c r="F17">
-        <v>-2.542876011786873</v>
+        <v>-2.371534013089615</v>
       </c>
       <c r="G17">
-        <v>-11.55764531555033</v>
+        <v>-14.08527000860266</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.50934305984923</v>
       </c>
       <c r="E18">
-        <v>-30.13505388240454</v>
+        <v>-33.74764628626057</v>
       </c>
       <c r="F18">
-        <v>-2.150282050006284</v>
+        <v>-2.113939086943261</v>
       </c>
       <c r="G18">
-        <v>-10.67781155921485</v>
+        <v>-13.48693690528971</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.02449349541338</v>
       </c>
       <c r="E19">
-        <v>-31.34212542186009</v>
+        <v>-34.13181032175327</v>
       </c>
       <c r="F19">
-        <v>-1.910036450744163</v>
+        <v>-2.014654283513324</v>
       </c>
       <c r="G19">
-        <v>-10.95685413217448</v>
+        <v>-13.02015495007078</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.477525791007215</v>
       </c>
       <c r="E20">
-        <v>-31.32811885175436</v>
+        <v>-35.46194993507827</v>
       </c>
       <c r="F20">
-        <v>-2.082121495001732</v>
+        <v>-2.060163960255726</v>
       </c>
       <c r="G20">
-        <v>-10.33402795768923</v>
+        <v>-12.47264699714949</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.865656152242685</v>
       </c>
       <c r="E21">
-        <v>-32.04046366281994</v>
+        <v>-35.68747699760827</v>
       </c>
       <c r="F21">
-        <v>-1.684556500436943</v>
+        <v>-1.793167892455</v>
       </c>
       <c r="G21">
-        <v>-10.31204262476293</v>
+        <v>-12.77024848840228</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.188729843512423</v>
       </c>
       <c r="E22">
-        <v>-32.63670519303985</v>
+        <v>-36.186784277457</v>
       </c>
       <c r="F22">
-        <v>-1.618463550469779</v>
+        <v>-1.802942627808034</v>
       </c>
       <c r="G22">
-        <v>-9.920223007462488</v>
+        <v>-12.76463380316767</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.44312437732014</v>
       </c>
       <c r="E23">
-        <v>-33.20631476762066</v>
+        <v>-36.52651492598644</v>
       </c>
       <c r="F23">
-        <v>-1.383152535826135</v>
+        <v>-1.656024213614917</v>
       </c>
       <c r="G23">
-        <v>-9.550941584193405</v>
+        <v>-12.1663784976749</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.624863800485105</v>
       </c>
       <c r="E24">
-        <v>-33.7713392622687</v>
+        <v>-36.81378320313701</v>
       </c>
       <c r="F24">
-        <v>-1.427548058411771</v>
+        <v>-1.459899118960703</v>
       </c>
       <c r="G24">
-        <v>-9.586556433104885</v>
+        <v>-11.86942256280227</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.732525263599016</v>
       </c>
       <c r="E25">
-        <v>-34.03445492329937</v>
+        <v>-37.60212712923632</v>
       </c>
       <c r="F25">
-        <v>-1.183267481530614</v>
+        <v>-1.592362521974969</v>
       </c>
       <c r="G25">
-        <v>-9.770470479993556</v>
+        <v>-12.00848864927044</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.764494378317603</v>
       </c>
       <c r="E26">
-        <v>-34.2381592695864</v>
+        <v>-37.36101305917192</v>
       </c>
       <c r="F26">
-        <v>-1.000134501221908</v>
+        <v>-1.333283989810202</v>
       </c>
       <c r="G26">
-        <v>-9.549531291793675</v>
+        <v>-11.82233667359722</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.719676922382077</v>
       </c>
       <c r="E27">
-        <v>-34.18601389138808</v>
+        <v>-37.16449540113505</v>
       </c>
       <c r="F27">
-        <v>-1.006400272256683</v>
+        <v>-1.422630869508754</v>
       </c>
       <c r="G27">
-        <v>-9.403423674963481</v>
+        <v>-12.61635115791818</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.599093647605522</v>
       </c>
       <c r="E28">
-        <v>-34.24876495571237</v>
+        <v>-37.97571944215811</v>
       </c>
       <c r="F28">
-        <v>-1.473983849910503</v>
+        <v>-1.484458555718903</v>
       </c>
       <c r="G28">
-        <v>-9.598653166505381</v>
+        <v>-12.49941606838004</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.402569410548195</v>
       </c>
       <c r="E29">
-        <v>-34.2539183591331</v>
+        <v>-37.70288567590698</v>
       </c>
       <c r="F29">
-        <v>-1.140980982352505</v>
+        <v>-1.351248793674714</v>
       </c>
       <c r="G29">
-        <v>-9.888309348463913</v>
+        <v>-11.99328993469964</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.132058102551051</v>
       </c>
       <c r="E30">
-        <v>-33.62891422625346</v>
+        <v>-37.7144695124186</v>
       </c>
       <c r="F30">
-        <v>-1.050945729342227</v>
+        <v>-1.140515439872132</v>
       </c>
       <c r="G30">
-        <v>-10.04550729285067</v>
+        <v>-12.64518600956523</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.793252466441371</v>
       </c>
       <c r="E31">
-        <v>-33.73115131968763</v>
+        <v>-37.55871264892478</v>
       </c>
       <c r="F31">
-        <v>-1.280825967293117</v>
+        <v>-1.417445289567228</v>
       </c>
       <c r="G31">
-        <v>-9.769550148333639</v>
+        <v>-12.77511830089055</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.389316727363806</v>
       </c>
       <c r="E32">
-        <v>-33.64679943434675</v>
+        <v>-36.87261260897066</v>
       </c>
       <c r="F32">
-        <v>-1.21186769447967</v>
+        <v>-1.532169204650543</v>
       </c>
       <c r="G32">
-        <v>-9.851105437693585</v>
+        <v>-12.6142787564106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.9285525634162128</v>
       </c>
       <c r="E33">
-        <v>-33.82086038977958</v>
+        <v>-37.03821890343117</v>
       </c>
       <c r="F33">
-        <v>-1.435000051567356</v>
+        <v>-1.572211656534469</v>
       </c>
       <c r="G33">
-        <v>-10.16870262400356</v>
+        <v>-12.43042429934163</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.4238743601523884</v>
       </c>
       <c r="E34">
-        <v>-32.78022838400195</v>
+        <v>-36.14856169259526</v>
       </c>
       <c r="F34">
-        <v>-1.188398389223554</v>
+        <v>-1.476343040273676</v>
       </c>
       <c r="G34">
-        <v>-10.00371827650845</v>
+        <v>-12.7179849059738</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.1178617690170831</v>
       </c>
       <c r="E35">
-        <v>-32.43756102007854</v>
+        <v>-35.92981375565474</v>
       </c>
       <c r="F35">
-        <v>-1.068316593778932</v>
+        <v>-1.38591182764486</v>
       </c>
       <c r="G35">
-        <v>-10.55573519245422</v>
+        <v>-12.3563475323549</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6848248286206866</v>
       </c>
       <c r="E36">
-        <v>-32.13448384016719</v>
+        <v>-35.91673099424658</v>
       </c>
       <c r="F36">
-        <v>-1.308135583828612</v>
+        <v>-1.53498234035045</v>
       </c>
       <c r="G36">
-        <v>-10.33274015547445</v>
+        <v>-12.5122510534358</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.263350037634287</v>
       </c>
       <c r="E37">
-        <v>-32.09215619361749</v>
+        <v>-34.85821378037566</v>
       </c>
       <c r="F37">
-        <v>-1.444862593865087</v>
+        <v>-1.159457717271948</v>
       </c>
       <c r="G37">
-        <v>-10.37463179872839</v>
+        <v>-12.95505969313209</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.848084148047039</v>
       </c>
       <c r="E38">
-        <v>-31.36476326342443</v>
+        <v>-34.5958136182382</v>
       </c>
       <c r="F38">
-        <v>-1.469474217769663</v>
+        <v>-1.302212756898595</v>
       </c>
       <c r="G38">
-        <v>-10.98984371847331</v>
+        <v>-13.27930114433939</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.432982430406312</v>
       </c>
       <c r="E39">
-        <v>-30.90549675075152</v>
+        <v>-34.00581685367487</v>
       </c>
       <c r="F39">
-        <v>-1.13741403231605</v>
+        <v>-1.251539866134544</v>
       </c>
       <c r="G39">
-        <v>-10.65441593388882</v>
+        <v>-12.99714334802731</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.009445510943851</v>
       </c>
       <c r="E40">
-        <v>-30.15158734100654</v>
+        <v>-34.43759552912121</v>
       </c>
       <c r="F40">
-        <v>-1.107398967843013</v>
+        <v>-1.33274803610059</v>
       </c>
       <c r="G40">
-        <v>-10.76112805880168</v>
+        <v>-12.8656352370253</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.573468581668134</v>
       </c>
       <c r="E41">
-        <v>-30.31419578567397</v>
+        <v>-33.38448984168946</v>
       </c>
       <c r="F41">
-        <v>-1.142303885094776</v>
+        <v>-1.153313716245384</v>
       </c>
       <c r="G41">
-        <v>-10.15643374223503</v>
+        <v>-12.74165861712513</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.122700291750579</v>
       </c>
       <c r="E42">
-        <v>-29.0978386102657</v>
+        <v>-32.42650475078882</v>
       </c>
       <c r="F42">
-        <v>-1.185803942517986</v>
+        <v>-1.158371727606878</v>
       </c>
       <c r="G42">
-        <v>-10.78822156349508</v>
+        <v>-12.55843316370863</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.650703727885608</v>
       </c>
       <c r="E43">
-        <v>-29.67585756107875</v>
+        <v>-31.90535890503809</v>
       </c>
       <c r="F43">
-        <v>-1.206821280261815</v>
+        <v>-0.8873903842312837</v>
       </c>
       <c r="G43">
-        <v>-10.46428468247739</v>
+        <v>-12.29705235120101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.152150446588325</v>
       </c>
       <c r="E44">
-        <v>-28.28674815922587</v>
+        <v>-31.80602909191685</v>
       </c>
       <c r="F44">
-        <v>-0.9722069226039252</v>
+        <v>-1.083287677849728</v>
       </c>
       <c r="G44">
-        <v>-10.58919487621963</v>
+        <v>-12.95648322771398</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.627457457797123</v>
       </c>
       <c r="E45">
-        <v>-28.41619911720913</v>
+        <v>-30.69753563889727</v>
       </c>
       <c r="F45">
-        <v>-0.8163603645434345</v>
+        <v>-1.181952034094968</v>
       </c>
       <c r="G45">
-        <v>-10.81832435408367</v>
+        <v>-13.07479881474199</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.072908422812858</v>
       </c>
       <c r="E46">
-        <v>-26.57793302090547</v>
+        <v>-30.83225774062547</v>
       </c>
       <c r="F46">
-        <v>-1.029918451189564</v>
+        <v>-0.9570138360691793</v>
       </c>
       <c r="G46">
-        <v>-10.6149707837884</v>
+        <v>-13.35427506916727</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.482338670307339</v>
       </c>
       <c r="E47">
-        <v>-26.67150940779997</v>
+        <v>-30.59920888276873</v>
       </c>
       <c r="F47">
-        <v>-0.9183936910158609</v>
+        <v>-0.9349179639669054</v>
       </c>
       <c r="G47">
-        <v>-10.83857827169293</v>
+        <v>-13.13280288313556</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.858523807722483</v>
       </c>
       <c r="E48">
-        <v>-25.63409035433078</v>
+        <v>-30.03585086655551</v>
       </c>
       <c r="F48">
-        <v>-0.8815255430194633</v>
+        <v>-1.005113817680136</v>
       </c>
       <c r="G48">
-        <v>-10.92244101129375</v>
+        <v>-12.90274645252053</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.201450245521368</v>
       </c>
       <c r="E49">
-        <v>-25.85399758061726</v>
+        <v>-29.08733707904191</v>
       </c>
       <c r="F49">
-        <v>-0.8014663186410994</v>
+        <v>-0.9192402825015219</v>
       </c>
       <c r="G49">
-        <v>-10.80581380249077</v>
+        <v>-12.82630595601876</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.504534150631334</v>
       </c>
       <c r="E50">
-        <v>-25.3040778110218</v>
+        <v>-27.96317963442981</v>
       </c>
       <c r="F50">
-        <v>-0.9020955623657806</v>
+        <v>-0.9669467895961482</v>
       </c>
       <c r="G50">
-        <v>-10.69513564402185</v>
+        <v>-12.84720874055371</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.770586322887883</v>
       </c>
       <c r="E51">
-        <v>-24.18194006581712</v>
+        <v>-29.11227991387616</v>
       </c>
       <c r="F51">
-        <v>-0.9662534460800051</v>
+        <v>-0.9138376703004636</v>
       </c>
       <c r="G51">
-        <v>-11.11440299438839</v>
+        <v>-13.10694421192832</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.001574147289666</v>
       </c>
       <c r="E52">
-        <v>-24.59661243069949</v>
+        <v>-27.18155596375789</v>
       </c>
       <c r="F52">
-        <v>-0.6895936441582206</v>
+        <v>-0.7197992331339018</v>
       </c>
       <c r="G52">
-        <v>-11.00838277349323</v>
+        <v>-12.86195722093117</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.18903018748059</v>
       </c>
       <c r="E53">
-        <v>-23.82400948025085</v>
+        <v>-26.79177662049567</v>
       </c>
       <c r="F53">
-        <v>-1.013598784987011</v>
+        <v>-0.9348682619227374</v>
       </c>
       <c r="G53">
-        <v>-11.0947284222485</v>
+        <v>-12.77176140771373</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.332757275091923</v>
       </c>
       <c r="E54">
-        <v>-23.23261794569315</v>
+        <v>-26.95976489228422</v>
       </c>
       <c r="F54">
-        <v>-0.8610764653139547</v>
+        <v>-0.6556380359500661</v>
       </c>
       <c r="G54">
-        <v>-10.83797906295032</v>
+        <v>-13.0230483668721</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.435658844889293</v>
       </c>
       <c r="E55">
-        <v>-22.71002298825998</v>
+        <v>-26.46615669697414</v>
       </c>
       <c r="F55">
-        <v>-1.024660803283995</v>
+        <v>-0.9086098436213959</v>
       </c>
       <c r="G55">
-        <v>-10.72335142365306</v>
+        <v>-13.22814990521211</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.490243272509655</v>
       </c>
       <c r="E56">
-        <v>-22.41508347614041</v>
+        <v>-26.37278861988399</v>
       </c>
       <c r="F56">
-        <v>-0.819932284784306</v>
+        <v>-1.018174686520075</v>
       </c>
       <c r="G56">
-        <v>-10.97322809041171</v>
+        <v>-13.13120388964009</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.493555137978603</v>
       </c>
       <c r="E57">
-        <v>-21.80870722109132</v>
+        <v>-26.58996517634385</v>
       </c>
       <c r="F57">
-        <v>-0.9607240936663184</v>
+        <v>-0.7353311219363925</v>
       </c>
       <c r="G57">
-        <v>-11.14892867381745</v>
+        <v>-13.23507556648027</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.44996756977336</v>
       </c>
       <c r="E58">
-        <v>-21.75734074042232</v>
+        <v>-25.30759643532576</v>
       </c>
       <c r="F58">
-        <v>-1.07407126212618</v>
+        <v>-0.9563337464314809</v>
       </c>
       <c r="G58">
-        <v>-11.2163644864524</v>
+        <v>-13.4338738261135</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.356499863132694</v>
       </c>
       <c r="E59">
-        <v>-21.26036336045053</v>
+        <v>-25.10975646287866</v>
       </c>
       <c r="F59">
-        <v>-1.014232486050152</v>
+        <v>-1.021689449410154</v>
       </c>
       <c r="G59">
-        <v>-11.44985064224612</v>
+        <v>-13.15255028727731</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.211244156589663</v>
       </c>
       <c r="E60">
-        <v>-21.16851232215296</v>
+        <v>-24.32220049125669</v>
       </c>
       <c r="F60">
-        <v>-1.070997190694391</v>
+        <v>-1.344828117935616</v>
       </c>
       <c r="G60">
-        <v>-11.34641595741713</v>
+        <v>-13.98733745045994</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.021281207327581</v>
       </c>
       <c r="E61">
-        <v>-20.55932388474511</v>
+        <v>-24.70161868598935</v>
       </c>
       <c r="F61">
-        <v>-1.005682906085859</v>
+        <v>-1.123663961796981</v>
       </c>
       <c r="G61">
-        <v>-11.53728877102935</v>
+        <v>-13.77906109894777</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.788416847634958</v>
       </c>
       <c r="E62">
-        <v>-19.941123784062</v>
+        <v>-24.468796251833</v>
       </c>
       <c r="F62">
-        <v>-1.404190582755034</v>
+        <v>-1.19187090537609</v>
       </c>
       <c r="G62">
-        <v>-11.17677036180272</v>
+        <v>-13.64108418196203</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.510561053424686</v>
       </c>
       <c r="E63">
-        <v>-20.80106288422257</v>
+        <v>-24.13084076511457</v>
       </c>
       <c r="F63">
-        <v>-1.233832684532301</v>
+        <v>-1.398014275399761</v>
       </c>
       <c r="G63">
-        <v>-11.8070684375701</v>
+        <v>-13.68434639106922</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.192638947836293</v>
       </c>
       <c r="E64">
-        <v>-20.20555043831789</v>
+        <v>-23.67786203860131</v>
       </c>
       <c r="F64">
-        <v>-1.232258786466982</v>
+        <v>-1.412226574929592</v>
       </c>
       <c r="G64">
-        <v>-11.79208159791382</v>
+        <v>-13.73958780921027</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.837523937802878</v>
       </c>
       <c r="E65">
-        <v>-19.76301437286632</v>
+        <v>-24.18697120043964</v>
       </c>
       <c r="F65">
-        <v>-1.438590195891089</v>
+        <v>-1.47637368986758</v>
       </c>
       <c r="G65">
-        <v>-11.71913372695598</v>
+        <v>-14.03349804218677</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.442020189948377</v>
       </c>
       <c r="E66">
-        <v>-18.92240732824449</v>
+        <v>-23.21063673285992</v>
       </c>
       <c r="F66">
-        <v>-1.52673262938597</v>
+        <v>-1.563624800037049</v>
       </c>
       <c r="G66">
-        <v>-11.91924296262277</v>
+        <v>-13.73261580030456</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.006295093120169</v>
       </c>
       <c r="E67">
-        <v>-19.44767408534219</v>
+        <v>-23.90625109670416</v>
       </c>
       <c r="F67">
-        <v>-1.590096937128313</v>
+        <v>-1.592429619734596</v>
       </c>
       <c r="G67">
-        <v>-12.03972033588792</v>
+        <v>-13.58245938627984</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.532544776378636</v>
       </c>
       <c r="E68">
-        <v>-20.05890033605349</v>
+        <v>-23.85579483931069</v>
       </c>
       <c r="F68">
-        <v>-1.761818328096053</v>
+        <v>-1.798489324650584</v>
       </c>
       <c r="G68">
-        <v>-11.55440429146739</v>
+        <v>-14.08823791267861</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.016999277882878</v>
       </c>
       <c r="E69">
-        <v>-19.45184028142925</v>
+        <v>-23.27012276742468</v>
       </c>
       <c r="F69">
-        <v>-1.908909042708953</v>
+        <v>-1.89395369761881</v>
       </c>
       <c r="G69">
-        <v>-11.70585512879796</v>
+        <v>-14.16048394798213</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.453807280444184</v>
       </c>
       <c r="E70">
-        <v>-19.35664270084</v>
+        <v>-23.88564201149525</v>
       </c>
       <c r="F70">
-        <v>-1.941801855539316</v>
+        <v>-1.911139836124692</v>
       </c>
       <c r="G70">
-        <v>-11.28217813177312</v>
+        <v>-13.43915745679418</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.844587478672641</v>
       </c>
       <c r="E71">
-        <v>-19.33206667240037</v>
+        <v>-22.948551299666</v>
       </c>
       <c r="F71">
-        <v>-2.080181458544376</v>
+        <v>-2.083442741009197</v>
       </c>
       <c r="G71">
-        <v>-11.52670164639476</v>
+        <v>-13.4728621209295</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.188578651962578</v>
       </c>
       <c r="E72">
-        <v>-19.17839290695008</v>
+        <v>-23.25236209236659</v>
       </c>
       <c r="F72">
-        <v>-2.133118277420278</v>
+        <v>-2.153475406344076</v>
       </c>
       <c r="G72">
-        <v>-11.56248864367429</v>
+        <v>-13.30182278564305</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.477489820239113</v>
       </c>
       <c r="E73">
-        <v>-19.14327006254659</v>
+        <v>-23.12258508425478</v>
       </c>
       <c r="F73">
-        <v>-2.125209853825751</v>
+        <v>-2.017447538395564</v>
       </c>
       <c r="G73">
-        <v>-11.3352859033141</v>
+        <v>-13.63798716661004</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.715457863786947</v>
       </c>
       <c r="E74">
-        <v>-20.01445789214221</v>
+        <v>-23.56730387417804</v>
       </c>
       <c r="F74">
-        <v>-2.140346611377107</v>
+        <v>-2.317822670692095</v>
       </c>
       <c r="G74">
-        <v>-11.22397874119273</v>
+        <v>-13.5775332945174</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9072340045149879</v>
       </c>
       <c r="E75">
-        <v>-20.43547012063533</v>
+        <v>-23.76142596946485</v>
       </c>
       <c r="F75">
-        <v>-2.103181079483104</v>
+        <v>-2.307100283030258</v>
       </c>
       <c r="G75">
-        <v>-10.68193318841124</v>
+        <v>-13.1388843552912</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.04783819514428351</v>
       </c>
       <c r="E76">
-        <v>-19.839581811388</v>
+        <v>-23.82458006797582</v>
       </c>
       <c r="F76">
-        <v>-2.481595048062572</v>
+        <v>-2.594727669365108</v>
       </c>
       <c r="G76">
-        <v>-11.15382828121557</v>
+        <v>-12.86112958454635</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8555011951651487</v>
       </c>
       <c r="E77">
-        <v>-19.71755302230331</v>
+        <v>-24.30496059070949</v>
       </c>
       <c r="F77">
-        <v>-2.625026035489903</v>
+        <v>-2.416857307166387</v>
       </c>
       <c r="G77">
-        <v>-10.72603627608541</v>
+        <v>-13.23938258622686</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.791049447047091</v>
       </c>
       <c r="E78">
-        <v>-20.41959329076443</v>
+        <v>-24.8123444039509</v>
       </c>
       <c r="F78">
-        <v>-2.53553667659807</v>
+        <v>-2.48663069350419</v>
       </c>
       <c r="G78">
-        <v>-10.6552237070004</v>
+        <v>-12.36921562286605</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.753089486637843</v>
       </c>
       <c r="E79">
-        <v>-21.18390913377904</v>
+        <v>-24.62219378036882</v>
       </c>
       <c r="F79">
-        <v>-2.349183832194682</v>
+        <v>-2.679718993259741</v>
       </c>
       <c r="G79">
-        <v>-10.04936407840392</v>
+        <v>-12.77863741079879</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.728062519256286</v>
       </c>
       <c r="E80">
-        <v>-21.50626402754104</v>
+        <v>-24.57946762810645</v>
       </c>
       <c r="F80">
-        <v>-2.400285817273383</v>
+        <v>-2.756375284347404</v>
       </c>
       <c r="G80">
-        <v>-10.0784041838744</v>
+        <v>-12.45765353640214</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.694637427329167</v>
       </c>
       <c r="E81">
-        <v>-22.15481396102356</v>
+        <v>-25.14458495647165</v>
       </c>
       <c r="F81">
-        <v>-2.745402729729922</v>
+        <v>-2.801720944344052</v>
       </c>
       <c r="G81">
-        <v>-9.735822310379543</v>
+        <v>-12.43466841872297</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.634520307007195</v>
       </c>
       <c r="E82">
-        <v>-22.18036361137484</v>
+        <v>-26.59874135897071</v>
       </c>
       <c r="F82">
-        <v>-2.621556832806979</v>
+        <v>-2.819394162882779</v>
       </c>
       <c r="G82">
-        <v>-9.824485341012304</v>
+        <v>-12.29311942310036</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>6.529176361760993</v>
       </c>
       <c r="E83">
-        <v>-23.08230883643056</v>
+        <v>-26.73276607570173</v>
       </c>
       <c r="F83">
-        <v>-2.605145217822715</v>
+        <v>-2.941037430881678</v>
       </c>
       <c r="G83">
-        <v>-9.361207598246695</v>
+        <v>-11.69524151979906</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>7.354419834461135</v>
       </c>
       <c r="E84">
-        <v>-23.87965989733112</v>
+        <v>-26.7921434268903</v>
       </c>
       <c r="F84">
-        <v>-3.032969645244367</v>
+        <v>-2.682208237305153</v>
       </c>
       <c r="G84">
-        <v>-9.343098914146882</v>
+        <v>-11.99775917117766</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>8.088230549146742</v>
       </c>
       <c r="E85">
-        <v>-24.24402544446228</v>
+        <v>-27.80852319011985</v>
       </c>
       <c r="F85">
-        <v>-2.925526251264257</v>
+        <v>-2.928528254732003</v>
       </c>
       <c r="G85">
-        <v>-9.596037835529357</v>
+        <v>-12.05021145470187</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>8.7158568976201</v>
       </c>
       <c r="E86">
-        <v>-25.23255509254466</v>
+        <v>-28.39571682927244</v>
       </c>
       <c r="F86">
-        <v>-2.94641436369325</v>
+        <v>-3.13580068952569</v>
       </c>
       <c r="G86">
-        <v>-9.277765297929365</v>
+        <v>-11.75392756057372</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>9.220079091905529</v>
       </c>
       <c r="E87">
-        <v>-26.15351537995858</v>
+        <v>-29.60353103846524</v>
       </c>
       <c r="F87">
-        <v>-2.891749570415107</v>
+        <v>-3.148244424650544</v>
       </c>
       <c r="G87">
-        <v>-9.03376816004846</v>
+        <v>-11.67351109887928</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>9.58479782143929</v>
       </c>
       <c r="E88">
-        <v>-26.29201422900918</v>
+        <v>-30.39833483273649</v>
       </c>
       <c r="F88">
-        <v>-3.063029441557156</v>
+        <v>-3.19937457422094</v>
       </c>
       <c r="G88">
-        <v>-9.068052169653152</v>
+        <v>-11.71582318141671</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>9.804087974144648</v>
       </c>
       <c r="E89">
-        <v>-28.21728136794821</v>
+        <v>-31.20368317873459</v>
       </c>
       <c r="F89">
-        <v>-3.186092531284453</v>
+        <v>-3.278963285914514</v>
       </c>
       <c r="G89">
-        <v>-9.463947068512436</v>
+        <v>-11.35950916502495</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>9.874671705722678</v>
       </c>
       <c r="E90">
-        <v>-29.59764855072928</v>
+        <v>-31.96235880737264</v>
       </c>
       <c r="F90">
-        <v>-3.240674487822315</v>
+        <v>-3.259706228901634</v>
       </c>
       <c r="G90">
-        <v>-9.291378261186848</v>
+        <v>-11.93565995795201</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>9.793569327184233</v>
       </c>
       <c r="E91">
-        <v>-30.42642948548007</v>
+        <v>-33.53038142455757</v>
       </c>
       <c r="F91">
-        <v>-3.553680566276733</v>
+        <v>-3.23811648928247</v>
       </c>
       <c r="G91">
-        <v>-8.869952435128704</v>
+        <v>-11.73068753088804</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>9.566881273612934</v>
       </c>
       <c r="E92">
-        <v>-32.2663847025886</v>
+        <v>-35.13793535559245</v>
       </c>
       <c r="F92">
-        <v>-3.491794065980985</v>
+        <v>-3.600849462926943</v>
       </c>
       <c r="G92">
-        <v>-9.105030963326811</v>
+        <v>-12.1026902225904</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>9.208948977250486</v>
       </c>
       <c r="E93">
-        <v>-33.39195955956511</v>
+        <v>-36.65186535075576</v>
       </c>
       <c r="F93">
-        <v>-3.274470221121729</v>
+        <v>-3.569662258578945</v>
       </c>
       <c r="G93">
-        <v>-9.118319493121446</v>
+        <v>-12.03347333645532</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>8.731019062778513</v>
       </c>
       <c r="E94">
-        <v>-35.1901531893749</v>
+        <v>-37.75315626586613</v>
       </c>
       <c r="F94">
-        <v>-3.287758890997439</v>
+        <v>-3.576277600657702</v>
       </c>
       <c r="G94">
-        <v>-9.59261804198729</v>
+        <v>-11.94201289484187</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.151176648101</v>
       </c>
       <c r="E95">
-        <v>-37.12794155894514</v>
+        <v>-38.89176180679971</v>
       </c>
       <c r="F95">
-        <v>-3.723517421403105</v>
+        <v>-3.822404608479699</v>
       </c>
       <c r="G95">
-        <v>-9.470869419235052</v>
+        <v>-12.45275723954955</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.489021177999346</v>
       </c>
       <c r="E96">
-        <v>-37.60066896060584</v>
+        <v>-41.22062919167236</v>
       </c>
       <c r="F96">
-        <v>-3.716693330738843</v>
+        <v>-4.167262241939161</v>
       </c>
       <c r="G96">
-        <v>-9.895135693365891</v>
+        <v>-11.94282066795346</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.77269134780851</v>
       </c>
       <c r="E97">
-        <v>-40.46524349940088</v>
+        <v>-42.21390241627777</v>
       </c>
       <c r="F97">
-        <v>-3.82493775599746</v>
+        <v>-4.101362301576849</v>
       </c>
       <c r="G97">
-        <v>-10.37905468756886</v>
+        <v>-12.60082800988454</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.996190353824537</v>
       </c>
       <c r="E98">
-        <v>-41.92193358310723</v>
+        <v>-44.03468407443782</v>
       </c>
       <c r="F98">
-        <v>-3.969870573526067</v>
+        <v>-4.1941709286517</v>
       </c>
       <c r="G98">
-        <v>-10.50986427346208</v>
+        <v>-12.85179384612561</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.211662124892634</v>
       </c>
       <c r="E99">
-        <v>-44.202457243711</v>
+        <v>-45.28702450431104</v>
       </c>
       <c r="F99">
-        <v>-3.882062800461917</v>
+        <v>-4.137051682759063</v>
       </c>
       <c r="G99">
-        <v>-10.66923393572259</v>
+        <v>-13.09343718612809</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.379327396854624</v>
       </c>
       <c r="E100">
-        <v>-45.70141836804194</v>
+        <v>-47.64186268761768</v>
       </c>
       <c r="F100">
-        <v>-3.858670533374261</v>
+        <v>-4.511657646387861</v>
       </c>
       <c r="G100">
-        <v>-10.60972025856312</v>
+        <v>-14.25122600121355</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.577664200599456</v>
       </c>
       <c r="E101">
-        <v>-47.43297323859186</v>
+        <v>-48.86410914347293</v>
       </c>
       <c r="F101">
-        <v>-4.216962629372325</v>
+        <v>-4.552723960381647</v>
       </c>
       <c r="G101">
-        <v>-11.12966791986997</v>
+        <v>-13.48479332705303</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.683811259208302</v>
       </c>
       <c r="E102">
-        <v>-49.92125762607503</v>
+        <v>-50.89890195476148</v>
       </c>
       <c r="F102">
-        <v>-4.156486838763545</v>
+        <v>-4.697299751559648</v>
       </c>
       <c r="G102">
-        <v>-11.33902350922794</v>
+        <v>-13.88540906385132</v>
       </c>
     </row>
   </sheetData>
